--- a/books_store/books_copy.xlsx
+++ b/books_store/books_copy.xlsx
@@ -3637,7 +3637,7 @@
         <v>240</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -4092,7 +4092,7 @@
         <v>93</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -4547,7 +4547,7 @@
         <v>37</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -4715,7 +4715,7 @@
         <v>52</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
